--- a/results/lendt_energy_fused.xlsx
+++ b/results/lendt_energy_fused.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Energy Expenditure" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Energy Expenditure matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -704,4 +705,890 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pred</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.51024935568834</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9770807593182821</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0627092678546106</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9615421635669685</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9926193550695956</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3" t="n">
+        <v>69</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>69</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1469766278834321</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.002261178890514341</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.00319347686932292</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.001469874067300224</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.003052483713728457</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D5" t="n">
+        <v>69</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.255602132525783</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01931695588501205</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05626063955663291</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.00537625198765972</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.03325765978236438</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.08717188390245266</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.001341105906191579</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.009193647000510721</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.003619180090575626</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>68</v>
+      </c>
+      <c r="D7" t="n">
+        <v>69</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>68</v>
+      </c>
+      <c r="D8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E8" t="n">
+        <v>66.03975672463828</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9711728930093865</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05783904388820978</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9571728618105243</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9851729242082486</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>68</v>
+      </c>
+      <c r="D9" t="n">
+        <v>69</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.029989437863065</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.01514690349798624</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05806957913274655</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.001091070881967382</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0292027361140051</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>68</v>
+      </c>
+      <c r="D10" t="n">
+        <v>69</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5070174051915641</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.007456138311640649</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.003879488613985921</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.006517102014007369</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.00839517460927393</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>68</v>
+      </c>
+      <c r="D11" t="n">
+        <v>69</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4232364323070822</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.006224065180986503</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00532664384621287</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.004934742691902125</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.007513387670070881</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" t="n">
+        <v>69</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="n">
+        <v>69</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>69</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
+        <v>69</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>69</v>
+      </c>
+      <c r="D17" t="n">
+        <v>69</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>69</v>
+      </c>
+      <c r="D18" t="n">
+        <v>69</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>69</v>
+      </c>
+      <c r="D19" t="n">
+        <v>69</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>69</v>
+      </c>
+      <c r="D20" t="n">
+        <v>69</v>
+      </c>
+      <c r="E20" t="n">
+        <v>69</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>69</v>
+      </c>
+      <c r="D21" t="n">
+        <v>69</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>69</v>
+      </c>
+      <c r="D22" t="n">
+        <v>69</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>69</v>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.06022403968132214</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0008728121692945238</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.006718889579256156</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.00248686568012768</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sedentary</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>69</v>
+      </c>
+      <c r="D24" t="n">
+        <v>69</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.004441976679622432</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.437647361771641e-05</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.000534751151963439</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0001928377266368825</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>69</v>
+      </c>
+      <c r="D25" t="n">
+        <v>69</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.030120321887152</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.02942203365053843</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.06350818818639435</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.01416570105275657</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0446783662483203</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>walk</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>69</v>
+      </c>
+      <c r="D26" t="n">
+        <v>69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>66.9052136617519</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.9696407777065493</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0651738872118536</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9539843005122058</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9852972549008928</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/lendt_energy_fused.xlsx
+++ b/results/lendt_energy_fused.xlsx
@@ -452,27 +452,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.98]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.98]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.98]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.98]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.98]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
     </row>
@@ -489,22 +489,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.91 [0.88, 0.94]</t>
+          <t>0.96 [0.94, 0.97]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.99]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.98 [0.98, 0.99]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.99 [0.98, 1.00]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
     </row>
@@ -516,27 +516,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.98]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.98]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.98]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.98]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.98]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.85 [0.81, 0.89]</t>
+          <t>0.92 [0.90, 0.94]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.99 [0.99, 1.00]</t>
+          <t>0.99 [0.99, 0.99]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -590,17 +590,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 0.99]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.97 [0.96, 0.99]</t>
+          <t>0.99 [0.98, 0.99]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.98 [0.96, 0.99]</t>
+          <t>1.00 [1.00, 1.00]</t>
         </is>
       </c>
     </row>
@@ -617,22 +617,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>356.65 ± 15.69</t>
+          <t>353.45 ± 30.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1694.70 ± 163.83</t>
+          <t>1685.36 ± 169.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1582.87 ± 258.25</t>
+          <t>1560.78 ± 285.01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1569.45 ± 332.17</t>
+          <t>1536.18 ± 332.84</t>
         </is>
       </c>
     </row>
@@ -646,16 +646,16 @@
         <v>7205</v>
       </c>
       <c r="C8" t="n">
-        <v>24609</v>
+        <v>23681</v>
       </c>
       <c r="D8" t="n">
-        <v>116934</v>
+        <v>112919</v>
       </c>
       <c r="E8" t="n">
-        <v>107635</v>
+        <v>106133</v>
       </c>
       <c r="F8" t="n">
-        <v>102014</v>
+        <v>99852</v>
       </c>
     </row>
     <row r="9">
@@ -668,10 +668,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
         <v>68</v>
@@ -781,19 +781,19 @@
         <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>63.51024935568834</v>
+        <v>64.75602389537951</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9770807593182821</v>
+        <v>0.9962465214673771</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0627092678546106</v>
+        <v>0.003006827353627396</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9615421635669685</v>
+        <v>0.9955014661296185</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9926193550695956</v>
+        <v>0.9969915768051357</v>
       </c>
     </row>
     <row r="3">
@@ -847,19 +847,19 @@
         <v>69</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1469766278834321</v>
+        <v>0.1275976004282059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002261178890514341</v>
+        <v>0.001963040006587783</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00319347686932292</v>
+        <v>0.002457853771038875</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001469874067300224</v>
+        <v>0.001354013662147585</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003052483713728457</v>
+        <v>0.002572066351027981</v>
       </c>
     </row>
     <row r="5">
@@ -880,19 +880,19 @@
         <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>1.255602132525783</v>
+        <v>0.1163785041922895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01931695588501205</v>
+        <v>0.001790438526035223</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05626063955663291</v>
+        <v>0.002244661864054234</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00537625198765972</v>
+        <v>0.001234238549585262</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03325765978236438</v>
+        <v>0.002346638502485185</v>
       </c>
     </row>
     <row r="6">
@@ -913,19 +913,19 @@
         <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08717188390245266</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001341105906191579</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009193647000510721</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003619180090575626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -979,19 +979,19 @@
         <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>66.03975672463828</v>
+        <v>67.02257008748339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9711728930093865</v>
+        <v>0.9856260306982851</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05783904388820978</v>
+        <v>0.00329773690665924</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9571728618105243</v>
+        <v>0.9848278083129341</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9851729242082486</v>
+        <v>0.9864242530836361</v>
       </c>
     </row>
     <row r="9">
@@ -1012,19 +1012,19 @@
         <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>1.029989437863065</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01514690349798624</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05806957913274655</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001091070881967382</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0292027361140051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1045,19 +1045,19 @@
         <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5070174051915641</v>
+        <v>0.3937263703719313</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007456138311640649</v>
+        <v>0.005790093681940166</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003879488613985921</v>
+        <v>0.002567097758969252</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006517102014007369</v>
+        <v>0.005168723647097238</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00839517460927393</v>
+        <v>0.006411463716783095</v>
       </c>
     </row>
     <row r="11">
@@ -1078,19 +1078,19 @@
         <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4232364323070822</v>
+        <v>0.583703542144682</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006224065180986503</v>
+        <v>0.008583875619774736</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00532664384621287</v>
+        <v>0.003567877500853047</v>
       </c>
       <c r="H11" t="n">
-        <v>0.004934742691902125</v>
+        <v>0.007720265280326454</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007513387670070881</v>
+        <v>0.009447485959223019</v>
       </c>
     </row>
     <row r="12">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>69</v>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D18" t="n">
         <v>69</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D19" t="n">
         <v>69</v>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D20" t="n">
         <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D21" t="n">
         <v>69</v>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D22" t="n">
         <v>69</v>
@@ -1468,25 +1468,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D23" t="n">
         <v>69</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06022403968132214</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0008728121692945238</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.006718889579256156</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00248686568012768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1501,25 +1501,25 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D24" t="n">
         <v>69</v>
       </c>
       <c r="E24" t="n">
-        <v>0.004441976679622432</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>6.437647361771641e-05</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000534751151963439</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0001928377266368825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1534,25 +1534,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D25" t="n">
         <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>2.030120321887152</v>
+        <v>0.9214565314905062</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02942203365053843</v>
+        <v>0.01375308255955979</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06350818818639435</v>
+        <v>0.03094810874296547</v>
       </c>
       <c r="H25" t="n">
-        <v>0.01416570105275657</v>
+        <v>0.006204245695447828</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0446783662483203</v>
+        <v>0.02130191942367176</v>
       </c>
     </row>
     <row r="26">
@@ -1567,25 +1567,25 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D26" t="n">
         <v>69</v>
       </c>
       <c r="E26" t="n">
-        <v>66.9052136617519</v>
+        <v>66.07854346850951</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9696407777065493</v>
+        <v>0.9862469174404405</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0651738872118536</v>
+        <v>0.03094810874296549</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9539843005122058</v>
+        <v>0.9786980805763285</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9852972549008928</v>
+        <v>0.9937957543045525</v>
       </c>
     </row>
   </sheetData>
